--- a/teacher_forms/009_senior_high_school_application_form--teacher_forms.xlsx
+++ b/teacher_forms/009_senior_high_school_application_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>student_government</t>
+          <t>debate_team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Student Government</t>
+          <t>Debate Team</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>debate_team</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Debate Team</t>
+          <t>Robotics</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>robotics</t>
+          <t>school_yearbook</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>School Yearbook</t>
         </is>
       </c>
     </row>
@@ -1076,29 +1076,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>school_yearbook</t>
+          <t>school_newspaper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>School Yearbook</t>
+          <t>School Newspaper</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>extracurricular_choices</t>
+          <t>school_choice_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>school_newspaper</t>
+          <t>school_of_choice_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>School Newspaper</t>
+          <t>School of Choice 1</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>school_of_choice_1</t>
+          <t>school_of_choice_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>School of Choice 1</t>
+          <t>School of Choice 2</t>
         </is>
       </c>
     </row>
@@ -1127,29 +1127,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>school_of_choice_2</t>
+          <t>school_of_choice_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>School of Choice 2</t>
+          <t>School of Choice 3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>school_choice_choices</t>
+          <t>uploaded_files_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>school_of_choice_3</t>
+          <t>file_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>School of Choice 3</t>
+          <t>File 1</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>file_1</t>
+          <t>file_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>File 1</t>
+          <t>File 2</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>file_2</t>
+          <t>file_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>File 2</t>
+          <t>File 3</t>
         </is>
       </c>
     </row>
@@ -1195,27 +1195,10 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>file_3</t>
+          <t>file_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>File 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>uploaded_files_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>file_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>File 4</t>
         </is>
